--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>877226</v>
+        <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>92234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>3277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Strömsund, Ly lm</t>
+          <t>Strömsund, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577438</v>
+        <v>576866</v>
       </c>
       <c r="R2" t="n">
-        <v>7249228</v>
+        <v>7249505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-05</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +774,243 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760033</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>877226</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO Strömsund, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>577438</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7249228</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Daniella Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/877226</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136760032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80594</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strömsund, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7249434</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760032</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92234</v>
+        <v>92239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92239</v>
+        <v>92241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92243</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92252</v>
+        <v>92256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92256</v>
+        <v>92258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92258</v>
+        <v>92271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>92273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92273</v>
+        <v>92276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92276</v>
+        <v>92286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136760032</v>
       </c>
       <c r="B4" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32807-2026 artfynd.xlsx
+++ b/artfynd/A 32807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760033</v>
       </c>
       <c r="B2" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
